--- a/buildplan_generator/output/25-075 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-075 GENERATED BUILD PLAN.xlsx
@@ -74,12 +74,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-        <bgColor rgb="00FCE4EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
@@ -88,6 +82,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>23-003, 23-002, 25-093, 25-092, 23-063</t>
+          <t>24-062, 23-101, 23-100, 24-045, 25-033</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,15 @@
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
-      <c r="F6" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -673,12 +671,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -722,8 +720,8 @@
       <c r="E9" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>7</v>
+      <c r="F9" s="9" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -732,7 +730,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>7.0-8.5</t>
+          <t>ratio=0.88 (0.50-1.50)</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -759,8 +757,8 @@
       <c r="E10" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F10" s="10" t="n">
-        <v>20.5</v>
+      <c r="F10" s="9" t="n">
+        <v>10.3</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -769,7 +767,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>9.0-26.0</t>
+          <t>ratio=1.29 (0.80-3.03)</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -797,16 +795,16 @@
         <v>3</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>2.0-8.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -833,8 +831,8 @@
       <c r="E12" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="10" t="n">
-        <v>2</v>
+      <c r="F12" s="9" t="n">
+        <v>1.6</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -843,7 +841,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=0.80 (0.50-1.00)</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -870,7 +868,7 @@
       <c r="E13" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="F13" s="9" t="n">
         <v>2</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -880,7 +878,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>1.0-4.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -907,8 +905,8 @@
       <c r="E14" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F14" s="10" t="n">
-        <v>5</v>
+      <c r="F14" s="9" t="n">
+        <v>3.5</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -917,7 +915,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>2.0-5.0</t>
+          <t>ratio=0.88 (0.50-1.25)</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -944,7 +942,7 @@
       <c r="E15" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F15" s="10" t="n">
+      <c r="F15" s="9" t="n">
         <v>4</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -954,7 +952,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>1.8-5.0</t>
+          <t>ratio=1.00 (0.83-1.25)</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -998,8 +996,8 @@
       <c r="E17" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="F17" s="10" t="n">
-        <v>20</v>
+      <c r="F17" s="9" t="n">
+        <v>19.9</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
@@ -1008,7 +1006,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>16.5-26.5</t>
+          <t>ratio=1.33 (0.50-1.86)</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1035,17 +1033,17 @@
       <c r="E18" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="F18" s="11" t="n">
-        <v>13</v>
+      <c r="F18" s="9" t="n">
+        <v>12.8</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>12.0-14.0</t>
+          <t>ratio=0.85 (0.60-1.12)</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1089,8 +1087,8 @@
       <c r="E20" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F20" s="10" t="n">
-        <v>8</v>
+      <c r="F20" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1099,7 +1097,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>6.0-8.0</t>
+          <t>ratio=1.00 (0.75-1.12)</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1143,7 +1141,7 @@
       <c r="E22" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="10" t="n">
+      <c r="F22" s="9" t="n">
         <v>2</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
@@ -1153,7 +1151,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=1.00 (0.75-1.00)</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1180,17 +1178,17 @@
       <c r="E23" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F23" s="11" t="n">
-        <v>2.5</v>
+      <c r="F23" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>2.5-2.5</t>
+          <t>ratio=1.00 (0.50-1.00)</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1217,17 +1215,17 @@
       <c r="E24" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F24" s="11" t="n">
-        <v>1.5</v>
+      <c r="F24" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1272,12 +1270,12 @@
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1304,8 +1302,8 @@
       <c r="E27" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F27" s="10" t="n">
-        <v>5</v>
+      <c r="F27" s="9" t="n">
+        <v>11</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1314,7 +1312,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>5.0-6.0</t>
+          <t>ratio=0.92 (0.62-3.07)</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1341,8 +1339,8 @@
       <c r="E28" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="F28" s="9" t="n">
-        <v>8.5</v>
+      <c r="F28" s="11" t="n">
+        <v>9</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1351,7 +1349,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-31.5</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1378,8 +1376,8 @@
       <c r="E29" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="F29" s="10" t="n">
-        <v>7</v>
+      <c r="F29" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
@@ -1388,7 +1386,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>4.0-29.0</t>
+          <t>ratio=1.00 (0.75-2.25)</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1432,17 +1430,17 @@
       <c r="E31" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F31" s="11" t="n">
-        <v>7.8</v>
+      <c r="F31" s="9" t="n">
+        <v>12</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>7.8-7.8</t>
+          <t>ratio=1.00 (0.80-1.96)</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1467,17 +1465,15 @@
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
-      <c r="F32" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1504,8 +1500,8 @@
       <c r="E33" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F33" s="10" t="n">
-        <v>5</v>
+      <c r="F33" s="9" t="n">
+        <v>2.4</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1514,7 +1510,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>2.0-12.5</t>
+          <t>ratio=1.20 (0.75-5.00)</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1546,12 +1542,12 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>5.0-5.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1578,8 +1574,8 @@
       <c r="E35" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F35" s="10" t="n">
-        <v>3.5</v>
+      <c r="F35" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1588,7 +1584,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>2.5-10.0</t>
+          <t>ratio=1.00 (0.83-1.50)</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1615,8 +1611,8 @@
       <c r="E36" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F36" s="10" t="n">
-        <v>13</v>
+      <c r="F36" s="9" t="n">
+        <v>13.7</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
@@ -1625,7 +1621,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>10.5-21.0</t>
+          <t>ratio=1.37 (0.88-1.67)</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1652,17 +1648,17 @@
       <c r="E37" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F37" s="10" t="n">
-        <v>3</v>
+      <c r="F37" s="11" t="n">
+        <v>6</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>3.0-12.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1706,17 +1702,17 @@
       <c r="E39" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="F39" s="11" t="n">
-        <v>4.5</v>
+      <c r="F39" s="9" t="n">
+        <v>8.5</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>4.5-4.5</t>
+          <t>ratio=0.95 (0.67-1.23)</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1743,8 +1739,8 @@
       <c r="E40" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F40" s="9" t="n">
-        <v>7</v>
+      <c r="F40" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1753,7 +1749,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-11.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1780,17 +1776,17 @@
       <c r="E41" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="11" t="n">
         <v>3</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>no data</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1834,8 +1830,8 @@
       <c r="E43" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="F43" s="10" t="n">
-        <v>6</v>
+      <c r="F43" s="9" t="n">
+        <v>12.2</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1844,7 +1840,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>5.0-7.0</t>
+          <t>ratio=0.88 (0.84-1.89)</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1871,8 +1867,8 @@
       <c r="E44" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="F44" s="10" t="n">
-        <v>4.5</v>
+      <c r="F44" s="9" t="n">
+        <v>14</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1881,7 +1877,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>3.5-5.5</t>
+          <t>ratio=2.00 (1.78-3.33)</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1908,8 +1904,8 @@
       <c r="E45" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F45" s="10" t="n">
-        <v>8.199999999999999</v>
+      <c r="F45" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
@@ -1918,7 +1914,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>3.0-12.0</t>
+          <t>ratio=2.33 (1.90-3.67)</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1945,17 +1941,17 @@
       <c r="E46" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F46" s="11" t="n">
-        <v>3</v>
+      <c r="F46" s="9" t="n">
+        <v>7</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>3.0-3.0</t>
+          <t>ratio=1.17 (1.00-1.67)</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1982,17 +1978,17 @@
       <c r="E47" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F47" s="11" t="n">
-        <v>8</v>
+      <c r="F47" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>8.0-8.0</t>
+          <t>ratio=1.00 (0.50-1.33)</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2019,8 +2015,8 @@
       <c r="E48" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F48" s="10" t="n">
-        <v>1</v>
+      <c r="F48" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -2029,7 +2025,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>0.5-4.0</t>
+          <t>ratio=1.00 (1.00-2.50)</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2054,17 +2050,15 @@
         </is>
       </c>
       <c r="E49" s="8" t="n"/>
-      <c r="F49" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2091,8 +2085,8 @@
       <c r="E50" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="F50" s="10" t="n">
-        <v>7</v>
+      <c r="F50" s="9" t="n">
+        <v>10.5</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2101,7 +2095,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>4.0-10.0</t>
+          <t>ratio=1.17 (0.65-1.50)</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2128,8 +2122,8 @@
       <c r="E51" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F51" s="10" t="n">
-        <v>25</v>
+      <c r="F51" s="9" t="n">
+        <v>12</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2138,7 +2132,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>16.5-33.5</t>
+          <t>ratio=1.20 (0.84-1.55)</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2165,8 +2159,8 @@
       <c r="E52" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F52" s="10" t="n">
-        <v>1</v>
+      <c r="F52" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
@@ -2175,7 +2169,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=2.50 (1.50-3.00)</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2219,8 +2213,8 @@
       <c r="E54" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F54" s="10" t="n">
-        <v>2</v>
+      <c r="F54" s="9" t="n">
+        <v>2.3</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -2229,7 +2223,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>1.5-2.0</t>
+          <t>ratio=0.76 (0.50-1.00)</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2256,8 +2250,8 @@
       <c r="E55" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F55" s="10" t="n">
-        <v>12</v>
+      <c r="F55" s="9" t="n">
+        <v>7.5</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -2266,7 +2260,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>6.0-25.0</t>
+          <t>ratio=0.62 (0.46-0.90)</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2293,17 +2287,17 @@
       <c r="E56" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F56" s="9" t="n">
-        <v>9.5</v>
+      <c r="F56" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>global:1.5-67.5</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2330,8 +2324,8 @@
       <c r="E57" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="F57" s="10" t="n">
-        <v>7</v>
+      <c r="F57" s="9" t="n">
+        <v>10.2</v>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
@@ -2340,7 +2334,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>2.0-9.0</t>
+          <t>ratio=1.45 (1.00-1.80)</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -2367,8 +2361,8 @@
       <c r="E58" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="F58" s="10" t="n">
-        <v>16.8</v>
+      <c r="F58" s="9" t="n">
+        <v>14.7</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
@@ -2377,7 +2371,7 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>4.5-20.5</t>
+          <t>ratio=0.61 (0.54-1.40)</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2404,17 +2398,17 @@
       <c r="E59" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F59" s="9" t="n">
-        <v>6</v>
+      <c r="F59" s="10" t="n">
+        <v>2.5</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-77.5</t>
+          <t>ratio=0.83 (n=2)</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2441,17 +2435,17 @@
       <c r="E60" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F60" s="11" t="n">
+      <c r="F60" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (0.50-1.00)</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2495,17 +2489,17 @@
       <c r="E62" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F62" s="11" t="n">
-        <v>2.8</v>
+      <c r="F62" s="9" t="n">
+        <v>1.5</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>1.5-4.0</t>
+          <t>ratio=1.50 (1.00-5.00)</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2530,17 +2524,15 @@
         </is>
       </c>
       <c r="E63" s="8" t="n"/>
-      <c r="F63" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I63" s="8" t="n"/>
@@ -2584,8 +2576,8 @@
       <c r="E65" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F65" s="10" t="n">
-        <v>2</v>
+      <c r="F65" s="9" t="n">
+        <v>2.5</v>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
@@ -2594,7 +2586,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>1.0-4.0</t>
+          <t>ratio=1.25 (1.00-1.50)</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
@@ -2621,8 +2613,8 @@
       <c r="E66" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F66" s="9" t="n">
-        <v>5</v>
+      <c r="F66" s="11" t="n">
+        <v>10</v>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
@@ -2631,7 +2623,7 @@
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-8.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2658,8 +2650,8 @@
       <c r="E67" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F67" s="10" t="n">
-        <v>7</v>
+      <c r="F67" s="9" t="n">
+        <v>12</v>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
@@ -2668,7 +2660,7 @@
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>6.5-11.0</t>
+          <t>ratio=1.00 (0.50-1.50)</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2696,12 +2688,12 @@
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2733,12 +2725,12 @@
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>3.0-3.0</t>
+          <t>wc_ratio=1.50</t>
         </is>
       </c>
       <c r="I69" s="8" t="n"/>
@@ -2766,12 +2758,12 @@
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I70" s="8" t="n"/>
@@ -2799,12 +2791,12 @@
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I71" s="8" t="n"/>
@@ -2848,8 +2840,8 @@
       <c r="E73" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F73" s="10" t="n">
-        <v>3</v>
+      <c r="F73" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
@@ -2858,7 +2850,7 @@
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>3.0-4.0</t>
+          <t>ratio=1.00 (1.00-2.00)</t>
         </is>
       </c>
       <c r="I73" s="8" t="n"/>
@@ -2886,12 +2878,12 @@
       <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I74" s="8" t="n"/>
@@ -2918,8 +2910,8 @@
       <c r="E75" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F75" s="10" t="n">
-        <v>4</v>
+      <c r="F75" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
@@ -2928,7 +2920,7 @@
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>3.5-7.5</t>
+          <t>ratio=1.25 (0.67-1.50)</t>
         </is>
       </c>
       <c r="I75" s="8" t="n"/>
@@ -2942,7 +2934,7 @@
         </is>
       </c>
       <c r="F77" s="1" t="n">
-        <v>312.6</v>
+        <v>335.1</v>
       </c>
     </row>
   </sheetData>
@@ -3010,7 +3002,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>23-003, 23-002, 25-093, 25-092, 23-063</t>
+          <t>24-062, 23-101, 23-100, 24-045, 25-033</t>
         </is>
       </c>
     </row>
@@ -4865,35 +4857,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>23-003</t>
+          <t>24-062</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23-002</t>
+          <t>23-101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25-093</t>
+          <t>23-100</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25-092</t>
+          <t>24-045</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23-063</t>
+          <t>25-033</t>
         </is>
       </c>
     </row>
@@ -4948,23 +4940,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4982,19 +4970,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>23-002, 23-003, 23-063, 25-092, 25-093</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5008,7 +4992,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5017,12 +5001,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>7.0-8.5</t>
+          <t>ratio=0.88 (0.50-1.50)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5022,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20.5</v>
+        <v>10.3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5047,12 +5031,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>9.0-26.0</t>
+          <t>ratio=1.29 (0.80-3.03)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -5068,21 +5052,21 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2.0-8.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>25-033</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5082,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5107,12 +5091,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=0.80 (0.50-1.00)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063</t>
+          <t>25-033, 24-062, 24-045, 23-101</t>
         </is>
       </c>
     </row>
@@ -5137,12 +5121,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.0-4.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063</t>
+          <t>24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5142,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5167,12 +5151,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2.0-5.0</t>
+          <t>ratio=0.88 (0.50-1.25)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063</t>
+          <t>24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5181,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.8-5.0</t>
+          <t>ratio=1.00 (0.83-1.25)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063</t>
+          <t>24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5202,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5227,12 +5211,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>16.5-26.5</t>
+          <t>ratio=1.33 (0.50-1.86)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -5248,21 +5232,21 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12.0-14.0</t>
+          <t>ratio=0.85 (0.60-1.12)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-093, 25-092</t>
+          <t>25-033, 24-062, 24-045</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5262,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5287,12 +5271,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6.0-8.0</t>
+          <t>ratio=1.00 (0.75-1.12)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>23-063, 23-003, 23-002</t>
+          <t>25-033, 24-062, 24-045, 23-101</t>
         </is>
       </c>
     </row>
@@ -5317,12 +5301,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=1.00 (0.75-1.00)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>25-033, 24-062, 24-045, 23-100</t>
         </is>
       </c>
     </row>
@@ -5338,21 +5322,21 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2.5-2.5</t>
+          <t>ratio=1.00 (0.50-1.00)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>23-063</t>
+          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -5368,21 +5352,21 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-093, 25-092</t>
+          <t>25-033, 24-062, 24-045</t>
         </is>
       </c>
     </row>
@@ -5402,19 +5386,15 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>23-002, 23-003, 23-063, 25-092, 25-093</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5428,7 +5408,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5437,12 +5417,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5.0-6.0</t>
+          <t>ratio=0.92 (0.62-3.07)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5438,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5467,12 +5447,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>global:1.0-31.5</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -5488,7 +5468,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5497,12 +5477,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4.0-29.0</t>
+          <t>ratio=1.00 (0.75-2.25)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -5518,21 +5498,21 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7.8-7.8</t>
+          <t>ratio=1.00 (0.80-1.96)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>23-063</t>
+          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -5548,23 +5528,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5578,7 +5554,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5587,12 +5563,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2.0-12.5</t>
+          <t>ratio=1.20 (0.75-5.00)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -5612,17 +5588,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>5.0-5.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>25-093, 25-092</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5614,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5647,12 +5623,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2.5-10.0</t>
+          <t>ratio=1.00 (0.83-1.50)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5644,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>13</v>
+        <v>13.7</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5677,12 +5653,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>10.5-21.0</t>
+          <t>ratio=1.37 (0.88-1.67)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>25-033, 24-062, 24-045, 23-100</t>
         </is>
       </c>
     </row>
@@ -5698,21 +5674,21 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3.0-12.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -5728,21 +5704,21 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>4.5-4.5</t>
+          <t>ratio=0.95 (0.67-1.23)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>23-063</t>
+          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -5758,23 +5734,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5788,7 +5760,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5797,12 +5769,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>global:1.0-11.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -5822,15 +5794,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>no data</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
+          <t>wc_ratio=1.00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>wc_avg</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5844,7 +5820,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>12.2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5853,12 +5829,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>5.0-7.0</t>
+          <t>ratio=0.88 (0.84-1.89)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5850,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5883,12 +5859,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3.5-5.5</t>
+          <t>ratio=2.00 (1.78-3.33)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-003, 23-002</t>
+          <t>24-062, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5880,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>8.199999999999999</v>
+        <v>18.7</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5913,12 +5889,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3.0-12.0</t>
+          <t>ratio=2.33 (1.90-3.67)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-003, 23-002</t>
+          <t>24-062, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -5934,21 +5910,21 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3.0-3.0</t>
+          <t>ratio=1.17 (1.00-1.67)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>23-063</t>
+          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -5964,21 +5940,21 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>8.0-8.0</t>
+          <t>ratio=1.00 (0.50-1.33)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>23-063</t>
+          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5970,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6003,12 +5979,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.5-4.0</t>
+          <t>ratio=1.00 (1.00-2.50)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -6024,23 +6000,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6054,7 +6026,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6063,12 +6035,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>4.0-10.0</t>
+          <t>ratio=1.17 (0.65-1.50)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6056,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6093,12 +6065,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>16.5-33.5</t>
+          <t>ratio=1.20 (0.84-1.55)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>24-062, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6086,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6123,12 +6095,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=2.50 (1.50-3.00)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6116,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,12 +6125,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.5-2.0</t>
+          <t>ratio=0.76 (0.50-1.00)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>25-033, 24-062, 24-045, 23-100</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6146,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>12</v>
+        <v>7.5</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6183,12 +6155,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>6.0-25.0</t>
+          <t>ratio=0.62 (0.46-0.90)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -6204,21 +6176,21 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>global:1.5-67.5</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>25-033</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6206,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>7</v>
+        <v>10.2</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6243,12 +6215,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2.0-9.0</t>
+          <t>ratio=1.45 (1.00-1.80)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6236,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>16.8</v>
+        <v>14.7</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6273,12 +6245,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>4.5-20.5</t>
+          <t>ratio=0.61 (0.54-1.40)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -6294,21 +6266,21 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>global:1.0-77.5</t>
+          <t>ratio=0.83 (n=2)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>25-033, 23-101</t>
         </is>
       </c>
     </row>
@@ -6328,17 +6300,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (0.50-1.00)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>24-062, 24-045, 23-101</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6326,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6363,12 +6335,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>global:1.0-8.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -6384,21 +6356,21 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.5-4.0</t>
+          <t>ratio=1.50 (1.00-5.00)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>24-062, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -6414,23 +6386,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6444,7 +6412,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6453,12 +6421,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.0-4.0</t>
+          <t>ratio=1.25 (1.00-1.50)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6442,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6483,12 +6451,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>6.5-11.0</t>
+          <t>ratio=1.00 (0.50-1.50)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -6508,19 +6476,15 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>23-002, 23-003, 23-063, 25-092, 25-093</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6538,17 +6502,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>3.0-3.0</t>
+          <t>wc_ratio=1.50</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -6568,19 +6532,15 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>23-002, 23-003, 23-063</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6598,19 +6558,15 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>23-002, 23-003, 23-063</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6624,7 +6580,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6633,12 +6589,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>3.0-4.0</t>
+          <t>ratio=1.00 (1.00-2.00)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -6658,19 +6614,15 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>23-002, 23-003, 23-063, 25-092, 25-093</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6684,7 +6636,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6693,12 +6645,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>3.5-7.5</t>
+          <t>ratio=1.25 (0.67-1.50)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>25-093, 25-092, 23-063, 23-003, 23-002</t>
+          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-075 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-075 GENERATED BUILD PLAN.xlsx
@@ -80,14 +80,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-        <bgColor rgb="00FCE4EC"/>
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>24-062, 23-101, 23-100, 24-045, 25-033</t>
+          <t>24-062, 23-101, 23-100, 23-096, 24-045</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
         <v>10</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.50-1.50)</t>
+          <t>ratio=1.00 (0.50-1.50)</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -758,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.29 (0.80-3.03)</t>
+          <t>ratio=1.33 (0.80-3.03)</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -799,12 +799,12 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -832,7 +832,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.80 (0.50-1.00)</t>
+          <t>ratio=0.75 (0.50-1.00)</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -906,7 +906,7 @@
         <v>4</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.50-1.25)</t>
+          <t>ratio=1.00 (0.50-1.25)</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.33 (0.50-1.86)</t>
+          <t>ratio=1.33 (0.74-1.86)</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1033,17 +1033,17 @@
       <c r="E18" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="F18" s="9" t="n">
-        <v>12.8</v>
+      <c r="F18" s="11" t="n">
+        <v>14.8</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.85 (0.60-1.12)</t>
+          <t>ratio=0.99 (n=2)</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-1.12)</t>
+          <t>ratio=1.00 (1.00-1.12)</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.00)</t>
+          <t>ratio=1.00 (0.50-1.33)</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>ratio=1.00 (1.00-2.13)</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1303,7 +1303,7 @@
         <v>12</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.92 (0.62-3.07)</t>
+          <t>ratio=0.88 (0.62-2.00)</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1339,7 +1339,7 @@
       <c r="E28" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="F28" s="11" t="n">
+      <c r="F28" s="10" t="n">
         <v>9</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-2.25)</t>
+          <t>ratio=1.00 (0.33-2.25)</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.80-1.96)</t>
+          <t>ratio=1.00 (0.83-1.96)</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1537,7 +1537,7 @@
       <c r="E34" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F34" s="11" t="n">
+      <c r="F34" s="10" t="n">
         <v>5</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.83-1.50)</t>
+          <t>ratio=1.00 (0.88-1.50)</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.37 (0.88-1.67)</t>
+          <t>ratio=1.37 (0.94-1.67)</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1648,7 +1648,7 @@
       <c r="E37" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F37" s="11" t="n">
+      <c r="F37" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.95 (0.67-1.23)</t>
+          <t>ratio=0.95 (0.45-1.23)</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1739,7 +1739,7 @@
       <c r="E40" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="F40" s="10" t="n">
         <v>2</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
@@ -1776,7 +1776,7 @@
       <c r="E41" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F41" s="11" t="n">
+      <c r="F41" s="10" t="n">
         <v>3</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
@@ -1905,7 +1905,7 @@
         <v>8</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>18.7</v>
+        <v>16.9</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.33 (1.90-3.67)</t>
+          <t>ratio=2.12 (1.67-3.67)</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -2016,7 +2016,7 @@
         <v>5</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-2.50)</t>
+          <t>ratio=1.25 (1.00-2.50)</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2086,7 +2086,7 @@
         <v>9</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.17 (0.65-1.50)</t>
+          <t>ratio=1.00 (0.65-1.50)</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2123,7 +2123,7 @@
         <v>10</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>12</v>
+        <v>10.2</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.20 (0.84-1.55)</t>
+          <t>ratio=1.02 (0.50-1.55)</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2160,7 +2160,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.50 (1.50-3.00)</t>
+          <t>ratio=2.75 (1.50-4.50)</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2214,7 +2214,7 @@
         <v>3</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.76 (0.50-1.00)</t>
+          <t>ratio=0.65 (0.50-0.85)</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.62 (0.46-0.90)</t>
+          <t>ratio=0.62 (0.46-0.83)</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2288,16 +2288,16 @@
         <v>3</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>wc_ratio=0.90</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.45 (1.00-1.80)</t>
+          <t>ratio=1.45 (0.80-1.80)</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.61 (0.54-1.40)</t>
+          <t>ratio=0.61 (0.39-0.81)</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2398,8 +2398,8 @@
       <c r="E59" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F59" s="10" t="n">
-        <v>2.5</v>
+      <c r="F59" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.83 (n=2)</t>
+          <t>ratio=0.67 (n=1)</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2436,7 +2436,7 @@
         <v>1</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.00)</t>
+          <t>ratio=0.75 (0.50-1.00)</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2490,7 +2490,7 @@
         <v>1</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.00-5.00)</t>
+          <t>ratio=1.25 (1.00-5.00)</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2577,7 +2577,7 @@
         <v>2</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.00-1.50)</t>
+          <t>ratio=1.12 (0.75-1.50)</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
@@ -2613,7 +2613,7 @@
       <c r="E66" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F66" s="11" t="n">
+      <c r="F66" s="10" t="n">
         <v>10</v>
       </c>
       <c r="G66" s="8" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.50)</t>
+          <t>ratio=1.00 (0.50-2.80)</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2720,7 +2720,7 @@
       <c r="E69" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F69" s="11" t="n">
+      <c r="F69" s="10" t="n">
         <v>3</v>
       </c>
       <c r="G69" s="8" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-2.00)</t>
+          <t>ratio=1.00 (1.00-5.00)</t>
         </is>
       </c>
       <c r="I73" s="8" t="n"/>
@@ -2911,7 +2911,7 @@
         <v>4</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (0.67-1.50)</t>
+          <t>ratio=1.17 (0.67-1.33)</t>
         </is>
       </c>
       <c r="I75" s="8" t="n"/>
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="F77" s="1" t="n">
-        <v>335.1</v>
+        <v>332.9</v>
       </c>
     </row>
   </sheetData>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>24-062, 23-101, 23-100, 24-045, 25-033</t>
+          <t>24-062, 23-101, 23-100, 23-096, 24-045</t>
         </is>
       </c>
     </row>
@@ -4878,14 +4878,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24-045</t>
+          <t>23-096</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25-033</t>
+          <t>24-045</t>
         </is>
       </c>
     </row>
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5001,12 +5001,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.50-1.50)</t>
+          <t>ratio=1.00 (0.50-1.50)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5031,12 +5031,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ratio=1.29 (0.80-3.03)</t>
+          <t>ratio=1.33 (0.80-3.03)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -5056,17 +5056,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-033</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5091,12 +5091,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ratio=0.80 (0.50-1.00)</t>
+          <t>ratio=0.75 (0.50-1.00)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101</t>
+          <t>24-062, 24-045, 23-101, 23-096</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5151,12 +5151,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.50-1.25)</t>
+          <t>ratio=1.00 (0.50-1.25)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -5211,12 +5211,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ratio=1.33 (0.50-1.86)</t>
+          <t>ratio=1.33 (0.74-1.86)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -5232,21 +5232,21 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>12.8</v>
+        <v>14.8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ratio=0.85 (0.60-1.12)</t>
+          <t>ratio=0.99 (n=2)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045</t>
+          <t>24-062, 24-045</t>
         </is>
       </c>
     </row>
@@ -5271,12 +5271,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-1.12)</t>
+          <t>ratio=1.00 (1.00-1.12)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101</t>
+          <t>24-062, 24-045, 23-101, 23-096</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-100</t>
+          <t>24-062, 24-045, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -5331,12 +5331,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.00)</t>
+          <t>ratio=1.00 (0.50-1.33)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -5361,12 +5361,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>ratio=1.00 (1.00-2.13)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045</t>
+          <t>24-062, 24-045, 23-096</t>
         </is>
       </c>
     </row>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5417,12 +5417,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ratio=0.92 (0.62-3.07)</t>
+          <t>ratio=0.88 (0.62-2.00)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -5477,12 +5477,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-2.25)</t>
+          <t>ratio=1.00 (0.33-2.25)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.80-1.96)</t>
+          <t>ratio=1.00 (0.83-1.96)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.83-1.50)</t>
+          <t>ratio=1.00 (0.88-1.50)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -5653,12 +5653,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ratio=1.37 (0.88-1.67)</t>
+          <t>ratio=1.37 (0.94-1.67)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-100</t>
+          <t>24-062, 24-045, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -5713,12 +5713,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ratio=0.95 (0.67-1.23)</t>
+          <t>ratio=0.95 (0.45-1.23)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>18.7</v>
+        <v>16.9</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5889,12 +5889,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ratio=2.33 (1.90-3.67)</t>
+          <t>ratio=2.12 (1.67-3.67)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>24-062, 23-101, 23-100</t>
+          <t>24-062, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -5970,7 +5970,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5979,12 +5979,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-2.50)</t>
+          <t>ratio=1.25 (1.00-2.50)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6035,12 +6035,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ratio=1.17 (0.65-1.50)</t>
+          <t>ratio=1.00 (0.65-1.50)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>12</v>
+        <v>10.2</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ratio=1.20 (0.84-1.55)</t>
+          <t>ratio=1.02 (0.50-1.55)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>24-062, 23-101, 23-100</t>
+          <t>24-062, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -6086,7 +6086,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ratio=2.50 (1.50-3.00)</t>
+          <t>ratio=2.75 (1.50-4.50)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6125,12 +6125,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ratio=0.76 (0.50-1.00)</t>
+          <t>ratio=0.65 (0.50-0.85)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-100</t>
+          <t>24-062, 24-045, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -6155,12 +6155,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ratio=0.62 (0.46-0.90)</t>
+          <t>ratio=0.62 (0.46-0.83)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -6176,21 +6176,21 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>wc_ratio=0.90</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>25-033</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -6215,12 +6215,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ratio=1.45 (1.00-1.80)</t>
+          <t>ratio=1.45 (0.80-1.80)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -6245,12 +6245,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ratio=0.61 (0.54-1.40)</t>
+          <t>ratio=0.61 (0.39-0.81)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6275,12 +6275,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ratio=0.83 (n=2)</t>
+          <t>ratio=0.67 (n=1)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>25-033, 23-101</t>
+          <t>23-101</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.00)</t>
+          <t>ratio=0.75 (0.50-1.00)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101</t>
+          <t>24-062, 24-045, 23-101, 23-096</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6365,12 +6365,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.00-5.00)</t>
+          <t>ratio=1.25 (1.00-5.00)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>24-062, 23-101, 23-100</t>
+          <t>24-062, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.00-1.50)</t>
+          <t>ratio=1.12 (0.75-1.50)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -6451,12 +6451,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.50)</t>
+          <t>ratio=1.00 (0.50-2.80)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -6589,12 +6589,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-2.00)</t>
+          <t>ratio=1.00 (1.00-5.00)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ratio=1.25 (0.67-1.50)</t>
+          <t>ratio=1.17 (0.67-1.33)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>25-033, 24-062, 24-045, 23-101, 23-100</t>
+          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-075 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-075 GENERATED BUILD PLAN.xlsx
@@ -80,14 +80,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-        <bgColor rgb="00FCE4EC"/>
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>24-062, 23-101, 23-100, 23-096, 24-045</t>
+          <t>24-062, 23-101, 23-100, 23-096, 25-033</t>
         </is>
       </c>
     </row>
@@ -638,12 +638,12 @@
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -671,12 +671,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -721,7 +721,7 @@
         <v>10</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.50)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -758,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>10.7</v>
+        <v>16.2</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.33 (0.80-3.03)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -794,17 +794,17 @@
       <c r="E11" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="10" t="n">
-        <v>3</v>
+      <c r="F11" s="9" t="n">
+        <v>2.5</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -832,7 +832,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.50-1.00)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -869,7 +869,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -906,7 +906,7 @@
         <v>4</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.25)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -943,7 +943,7 @@
         <v>4</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.83-1.25)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -997,7 +997,7 @@
         <v>15</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>19.9</v>
+        <v>21.1</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.33 (0.74-1.86)</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1033,17 +1033,17 @@
       <c r="E18" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="F18" s="11" t="n">
-        <v>14.8</v>
+      <c r="F18" s="9" t="n">
+        <v>4.9</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.99 (n=2)</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1088,7 +1088,7 @@
         <v>3</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.12)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1142,7 +1142,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-1.00)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1179,7 +1179,7 @@
         <v>3</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.33)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1216,7 +1216,7 @@
         <v>2</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-2.13)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1270,12 +1270,12 @@
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1303,7 +1303,7 @@
         <v>12</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>10.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.62-2.00)</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1339,17 +1339,17 @@
       <c r="E28" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="F28" s="10" t="n">
-        <v>9</v>
+      <c r="F28" s="9" t="n">
+        <v>1.9</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1377,7 +1377,7 @@
         <v>15</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>15</v>
+        <v>8.1</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.33-2.25)</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1431,7 +1431,7 @@
         <v>12</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.83-1.96)</t>
+          <t>group_total:32h</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1468,12 +1468,12 @@
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1501,7 +1501,7 @@
         <v>2</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.20 (0.75-5.00)</t>
+          <t>group_total:32h</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1537,17 +1537,17 @@
       <c r="E34" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F34" s="10" t="n">
-        <v>5</v>
+      <c r="F34" s="9" t="n">
+        <v>0.4</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:32h</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1575,7 +1575,7 @@
         <v>4</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.88-1.50)</t>
+          <t>group_total:32h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1612,7 +1612,7 @@
         <v>10</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>13.7</v>
+        <v>11.2</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.37 (0.94-1.67)</t>
+          <t>group_total:32h</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1648,17 +1648,17 @@
       <c r="E37" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F37" s="10" t="n">
-        <v>6</v>
+      <c r="F37" s="9" t="n">
+        <v>2.1</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:32h</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1703,7 +1703,7 @@
         <v>9</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.95 (0.45-1.23)</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1739,17 +1739,17 @@
       <c r="E40" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F40" s="10" t="n">
-        <v>2</v>
+      <c r="F40" s="9" t="n">
+        <v>0.6</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1777,16 +1777,16 @@
         <v>3</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1831,7 +1831,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>12.2</v>
+        <v>14.8</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.84-1.89)</t>
+          <t>group_total:74h</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1868,7 +1868,7 @@
         <v>7</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>14</v>
+        <v>8.6</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.00 (1.78-3.33)</t>
+          <t>group_total:74h</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1905,7 +1905,7 @@
         <v>8</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>16.9</v>
+        <v>10.1</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.12 (1.67-3.67)</t>
+          <t>group_total:74h</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1942,7 +1942,7 @@
         <v>6</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.17 (1.00-1.67)</t>
+          <t>group_total:74h</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1979,7 +1979,7 @@
         <v>6</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.33)</t>
+          <t>group_total:74h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2016,7 +2016,7 @@
         <v>5</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.00-2.50)</t>
+          <t>group_total:74h</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2053,12 +2053,12 @@
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2086,7 +2086,7 @@
         <v>9</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.65-1.50)</t>
+          <t>group_total:74h</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2123,7 +2123,7 @@
         <v>10</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>10.2</v>
+        <v>20.5</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.02 (0.50-1.55)</t>
+          <t>group_total:74h</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2159,17 +2159,17 @@
       <c r="E52" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F52" s="9" t="n">
-        <v>5.5</v>
+      <c r="F52" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.75 (1.50-4.50)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2214,7 +2214,7 @@
         <v>3</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.65 (0.50-0.85)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2251,7 +2251,7 @@
         <v>12</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.62 (0.46-0.83)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2287,17 +2287,17 @@
       <c r="E56" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F56" s="10" t="n">
-        <v>2.7</v>
+      <c r="F56" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=0.90</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2325,7 +2325,7 @@
         <v>7</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>10.2</v>
+        <v>5.5</v>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.45 (0.80-1.80)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -2362,7 +2362,7 @@
         <v>24</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>14.7</v>
+        <v>10.9</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.61 (0.39-0.81)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2398,17 +2398,17 @@
       <c r="E59" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F59" s="11" t="n">
-        <v>2</v>
+      <c r="F59" s="9" t="n">
+        <v>3.3</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.67 (n=1)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2436,7 +2436,7 @@
         <v>1</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.50-1.00)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.00-5.00)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2527,12 +2527,12 @@
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I63" s="8" t="n"/>
@@ -2577,7 +2577,7 @@
         <v>2</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.12 (0.75-1.50)</t>
+          <t>group_total:51h</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
@@ -2613,17 +2613,17 @@
       <c r="E66" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F66" s="10" t="n">
-        <v>10</v>
+      <c r="F66" s="9" t="n">
+        <v>0.3</v>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:51h</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2651,7 +2651,7 @@
         <v>12</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>12</v>
+        <v>25.3</v>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-2.80)</t>
+          <t>group_total:51h</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2688,12 +2688,12 @@
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2720,17 +2720,17 @@
       <c r="E69" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F69" s="10" t="n">
-        <v>3</v>
+      <c r="F69" s="9" t="n">
+        <v>1.3</v>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.50</t>
+          <t>group_total:51h</t>
         </is>
       </c>
       <c r="I69" s="8" t="n"/>
@@ -2758,12 +2758,12 @@
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I70" s="8" t="n"/>
@@ -2791,12 +2791,12 @@
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I71" s="8" t="n"/>
@@ -2841,7 +2841,7 @@
         <v>2</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>2</v>
+        <v>8.4</v>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-5.00)</t>
+          <t>group_total:51h</t>
         </is>
       </c>
       <c r="I73" s="8" t="n"/>
@@ -2878,12 +2878,12 @@
       <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I74" s="8" t="n"/>
@@ -2911,7 +2911,7 @@
         <v>4</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.17 (0.67-1.33)</t>
+          <t>group_total:51h</t>
         </is>
       </c>
       <c r="I75" s="8" t="n"/>
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="F77" s="1" t="n">
-        <v>332.9</v>
+        <v>301.9</v>
       </c>
     </row>
   </sheetData>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>24-062, 23-101, 23-100, 23-096, 24-045</t>
+          <t>24-062, 23-101, 23-100, 23-096, 25-033</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>24-045</t>
+          <t>25-033</t>
         </is>
       </c>
     </row>
@@ -4944,15 +4944,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4970,15 +4974,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4992,7 +5000,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5001,12 +5009,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.50)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5030,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10.7</v>
+        <v>16.2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5031,12 +5039,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ratio=1.33 (0.80-3.03)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5052,21 +5060,21 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5090,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5091,12 +5099,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.50-1.00)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-096</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5120,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5121,12 +5129,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5150,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5151,12 +5159,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.25)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5180,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5181,12 +5189,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.83-1.25)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5210,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>19.9</v>
+        <v>21.1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5211,12 +5219,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ratio=1.33 (0.74-1.86)</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -5232,21 +5240,21 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>14.8</v>
+        <v>4.9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ratio=0.99 (n=2)</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>24-062, 24-045</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5270,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5271,12 +5279,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.12)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-096</t>
+          <t>model(SUPPORTS)</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5300,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5301,12 +5309,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-1.00)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-100, 23-096</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5330,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5331,12 +5339,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.33)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5360,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5361,12 +5369,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-2.13)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-096</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -5386,15 +5394,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5408,7 +5420,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5417,12 +5429,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.62-2.00)</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -5438,21 +5450,21 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>1.9</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5480,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>15</v>
+        <v>8.1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5477,12 +5489,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.33-2.25)</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5510,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5507,12 +5519,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.83-1.96)</t>
+          <t>group_total:32h</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5532,15 +5544,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5554,7 +5570,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5563,12 +5579,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ratio=1.20 (0.75-5.00)</t>
+          <t>group_total:32h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5584,21 +5600,21 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>0.4</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:32h</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5630,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5623,12 +5639,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.88-1.50)</t>
+          <t>group_total:32h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5660,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>13.7</v>
+        <v>11.2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5653,12 +5669,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ratio=1.37 (0.94-1.67)</t>
+          <t>group_total:32h</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-100, 23-096</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5674,21 +5690,21 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:32h</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5720,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5713,12 +5729,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ratio=0.95 (0.45-1.23)</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5738,15 +5754,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5760,21 +5780,21 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5790,21 +5810,21 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5820,7 +5840,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>12.2</v>
+        <v>14.8</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5829,12 +5849,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.84-1.89)</t>
+          <t>group_total:74h</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5870,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>14</v>
+        <v>8.6</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5859,12 +5879,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ratio=2.00 (1.78-3.33)</t>
+          <t>group_total:74h</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>24-062, 23-101, 23-100</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5900,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>16.9</v>
+        <v>10.1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5889,12 +5909,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ratio=2.12 (1.67-3.67)</t>
+          <t>group_total:74h</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>24-062, 23-101, 23-100, 23-096</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5930,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5919,12 +5939,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ratio=1.17 (1.00-1.67)</t>
+          <t>group_total:74h</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5960,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5949,12 +5969,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.33)</t>
+          <t>group_total:74h</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5970,7 +5990,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5979,12 +5999,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.00-2.50)</t>
+          <t>group_total:74h</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6004,15 +6024,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6026,7 +6050,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6035,12 +6059,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.65-1.50)</t>
+          <t>group_total:74h</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6080,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>10.2</v>
+        <v>20.5</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6065,12 +6089,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ratio=1.02 (0.50-1.55)</t>
+          <t>group_total:74h</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>24-062, 23-101, 23-100, 23-096</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6086,21 +6110,21 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ratio=2.75 (1.50-4.50)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6140,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6125,12 +6149,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ratio=0.65 (0.50-0.85)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-100, 23-096</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6170,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6155,12 +6179,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ratio=0.62 (0.46-0.83)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6176,21 +6200,21 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>wc_ratio=0.90</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6230,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>10.2</v>
+        <v>5.5</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6215,12 +6239,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ratio=1.45 (0.80-1.80)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6260,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>14.7</v>
+        <v>10.9</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6245,12 +6269,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ratio=0.61 (0.39-0.81)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6266,21 +6290,21 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ratio=0.67 (n=1)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>23-101</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6320,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6305,12 +6329,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.50-1.00)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-096</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6326,21 +6350,21 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>10</v>
+        <v>0.3</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:51h</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6365,12 +6389,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.00-5.00)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>24-062, 23-101, 23-100, 23-096</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6390,15 +6414,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6412,7 +6440,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6421,12 +6449,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ratio=1.12 (0.75-1.50)</t>
+          <t>group_total:51h</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6470,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>12</v>
+        <v>25.3</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6451,12 +6479,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-2.80)</t>
+          <t>group_total:51h</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6476,15 +6504,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6498,21 +6530,21 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>wc_ratio=1.50</t>
+          <t>group_total:51h</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6532,15 +6564,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6558,15 +6594,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6580,7 +6620,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>8.4</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6589,12 +6629,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-5.00)</t>
+          <t>group_total:51h</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6614,15 +6654,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6636,7 +6680,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6645,12 +6689,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ratio=1.17 (0.67-1.33)</t>
+          <t>group_total:51h</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>24-062, 24-045, 23-101, 23-100, 23-096</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-075 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-075 GENERATED BUILD PLAN.xlsx
@@ -721,7 +721,7 @@
         <v>10</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -758,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>16.2</v>
+        <v>17.5</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -795,7 +795,7 @@
         <v>3</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -832,7 +832,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -869,7 +869,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -906,7 +906,7 @@
         <v>4</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -943,7 +943,7 @@
         <v>4</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -997,7 +997,7 @@
         <v>15</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>21.1</v>
+        <v>19.3</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>group_total:26h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1034,7 +1034,7 @@
         <v>15</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>group_total:26h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1088,7 +1088,7 @@
         <v>3</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1179,7 +1179,7 @@
         <v>3</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1216,7 +1216,7 @@
         <v>2</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1303,7 +1303,7 @@
         <v>12</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>8.699999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>group_total:19h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1340,7 +1340,7 @@
         <v>9</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>group_total:19h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1377,7 +1377,7 @@
         <v>15</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>8.1</v>
+        <v>10.5</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>group_total:19h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1431,7 +1431,7 @@
         <v>12</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>group_total:32h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1501,7 +1501,7 @@
         <v>2</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>group_total:32h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>group_total:32h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1575,7 +1575,7 @@
         <v>4</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>group_total:32h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1612,7 +1612,7 @@
         <v>10</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>11.2</v>
+        <v>10.2</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>group_total:32h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1649,7 +1649,7 @@
         <v>6</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>group_total:32h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1703,7 +1703,7 @@
         <v>9</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>10.5</v>
+        <v>14.3</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>group_total:11h</t>
+          <t>group_total:15h</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1740,7 +1740,7 @@
         <v>2</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>group_total:11h</t>
+          <t>group_total:15h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1777,7 +1777,7 @@
         <v>3</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>group_total:11h</t>
+          <t>group_total:15h</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1831,7 +1831,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>14.8</v>
+        <v>16.4</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>group_total:74h</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1868,7 +1868,7 @@
         <v>7</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>group_total:74h</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1905,7 +1905,7 @@
         <v>8</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>10.1</v>
+        <v>11.2</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>group_total:74h</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1942,7 +1942,7 @@
         <v>6</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>group_total:74h</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1979,7 +1979,7 @@
         <v>6</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>group_total:74h</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2016,7 +2016,7 @@
         <v>5</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>group_total:74h</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2086,7 +2086,7 @@
         <v>9</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>group_total:74h</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2123,7 +2123,7 @@
         <v>10</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>20.5</v>
+        <v>22.8</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>group_total:74h</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2362,7 +2362,7 @@
         <v>24</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>2</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>group_total:51h</t>
+          <t>group_total:53h</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>group_total:51h</t>
+          <t>group_total:53h</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2651,7 +2651,7 @@
         <v>12</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>25.3</v>
+        <v>26.5</v>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>group_total:51h</t>
+          <t>group_total:53h</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2721,7 +2721,7 @@
         <v>2</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>group_total:51h</t>
+          <t>group_total:53h</t>
         </is>
       </c>
       <c r="I69" s="8" t="n"/>
@@ -2841,7 +2841,7 @@
         <v>2</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>group_total:51h</t>
+          <t>group_total:53h</t>
         </is>
       </c>
       <c r="I73" s="8" t="n"/>
@@ -2911,7 +2911,7 @@
         <v>4</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>group_total:51h</t>
+          <t>group_total:53h</t>
         </is>
       </c>
       <c r="I75" s="8" t="n"/>
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="F77" s="1" t="n">
-        <v>301.9</v>
+        <v>322.4</v>
       </c>
     </row>
   </sheetData>
@@ -5000,7 +5000,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.2</v>
+        <v>17.5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -5120,7 +5120,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -5180,7 +5180,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21.1</v>
+        <v>19.3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>group_total:26h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>group_total:26h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5360,7 +5360,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5420,7 +5420,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8.699999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>group_total:19h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>group_total:19h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8.1</v>
+        <v>10.5</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>group_total:19h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>group_total:32h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -5570,7 +5570,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>group_total:32h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>group_total:32h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>group_total:32h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>11.2</v>
+        <v>10.2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>group_total:32h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>group_total:32h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10.5</v>
+        <v>14.3</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>group_total:11h</t>
+          <t>group_total:15h</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -5780,7 +5780,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>group_total:11h</t>
+          <t>group_total:15h</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>group_total:11h</t>
+          <t>group_total:15h</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>14.8</v>
+        <v>16.4</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>group_total:74h</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5870,7 +5870,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>group_total:74h</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>10.1</v>
+        <v>11.2</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>group_total:74h</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>group_total:74h</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>group_total:74h</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>group_total:74h</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6050,7 +6050,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>group_total:74h</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>20.5</v>
+        <v>22.8</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>group_total:74h</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6260,7 +6260,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>group_total:51h</t>
+          <t>group_total:53h</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>group_total:51h</t>
+          <t>group_total:53h</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6470,7 +6470,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>25.3</v>
+        <v>26.5</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>group_total:51h</t>
+          <t>group_total:53h</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>group_total:51h</t>
+          <t>group_total:53h</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -6620,7 +6620,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>group_total:51h</t>
+          <t>group_total:53h</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>group_total:51h</t>
+          <t>group_total:53h</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
